--- a/src/test/output_test/Specific_Regions/Region_-200_200_0/Files/1.xlsx
+++ b/src/test/output_test/Specific_Regions/Region_-200_200_0/Files/1.xlsx
@@ -393,7 +393,7 @@
         <v>-199</v>
       </c>
       <c r="B2">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -401,7 +401,7 @@
         <v>-198</v>
       </c>
       <c r="B3">
-        <v>33</v>
+        <v>29</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -409,7 +409,7 @@
         <v>-197</v>
       </c>
       <c r="B4">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -417,7 +417,7 @@
         <v>-196</v>
       </c>
       <c r="B5">
-        <v>29</v>
+        <v>39</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -425,7 +425,7 @@
         <v>-195</v>
       </c>
       <c r="B6">
-        <v>32</v>
+        <v>37</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -433,7 +433,7 @@
         <v>-194</v>
       </c>
       <c r="B7">
-        <v>29</v>
+        <v>38</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -441,7 +441,7 @@
         <v>-193</v>
       </c>
       <c r="B8">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -449,7 +449,7 @@
         <v>-192</v>
       </c>
       <c r="B9">
-        <v>25</v>
+        <v>30</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -457,7 +457,7 @@
         <v>-191</v>
       </c>
       <c r="B10">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -465,7 +465,7 @@
         <v>-190</v>
       </c>
       <c r="B11">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -473,7 +473,7 @@
         <v>-189</v>
       </c>
       <c r="B12">
-        <v>23</v>
+        <v>33</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -489,7 +489,7 @@
         <v>-187</v>
       </c>
       <c r="B14">
-        <v>26</v>
+        <v>36</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -497,7 +497,7 @@
         <v>-186</v>
       </c>
       <c r="B15">
-        <v>27</v>
+        <v>34</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -505,7 +505,7 @@
         <v>-185</v>
       </c>
       <c r="B16">
-        <v>34</v>
+        <v>49</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -513,7 +513,7 @@
         <v>-184</v>
       </c>
       <c r="B17">
-        <v>24</v>
+        <v>32</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -521,7 +521,7 @@
         <v>-183</v>
       </c>
       <c r="B18">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -529,7 +529,7 @@
         <v>-182</v>
       </c>
       <c r="B19">
-        <v>24</v>
+        <v>32</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -537,7 +537,7 @@
         <v>-181</v>
       </c>
       <c r="B20">
-        <v>27</v>
+        <v>40</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -545,7 +545,7 @@
         <v>-180</v>
       </c>
       <c r="B21">
-        <v>28</v>
+        <v>34</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -553,7 +553,7 @@
         <v>-179</v>
       </c>
       <c r="B22">
-        <v>32</v>
+        <v>37</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -561,7 +561,7 @@
         <v>-178</v>
       </c>
       <c r="B23">
-        <v>25</v>
+        <v>37</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -569,7 +569,7 @@
         <v>-177</v>
       </c>
       <c r="B24">
-        <v>29</v>
+        <v>36</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -577,7 +577,7 @@
         <v>-176</v>
       </c>
       <c r="B25">
-        <v>18</v>
+        <v>32</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -585,7 +585,7 @@
         <v>-175</v>
       </c>
       <c r="B26">
-        <v>21</v>
+        <v>37</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -593,7 +593,7 @@
         <v>-174</v>
       </c>
       <c r="B27">
-        <v>32</v>
+        <v>29</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -601,7 +601,7 @@
         <v>-173</v>
       </c>
       <c r="B28">
-        <v>41</v>
+        <v>33</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -609,7 +609,7 @@
         <v>-172</v>
       </c>
       <c r="B29">
-        <v>32</v>
+        <v>24</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -617,7 +617,7 @@
         <v>-171</v>
       </c>
       <c r="B30">
-        <v>34</v>
+        <v>31</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -625,7 +625,7 @@
         <v>-170</v>
       </c>
       <c r="B31">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -633,7 +633,7 @@
         <v>-169</v>
       </c>
       <c r="B32">
-        <v>25</v>
+        <v>28</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -641,7 +641,7 @@
         <v>-168</v>
       </c>
       <c r="B33">
-        <v>29</v>
+        <v>38</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -649,7 +649,7 @@
         <v>-167</v>
       </c>
       <c r="B34">
-        <v>39</v>
+        <v>29</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -657,7 +657,7 @@
         <v>-166</v>
       </c>
       <c r="B35">
-        <v>27</v>
+        <v>46</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -665,7 +665,7 @@
         <v>-165</v>
       </c>
       <c r="B36">
-        <v>28</v>
+        <v>34</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -673,7 +673,7 @@
         <v>-164</v>
       </c>
       <c r="B37">
-        <v>38</v>
+        <v>15</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -681,7 +681,7 @@
         <v>-163</v>
       </c>
       <c r="B38">
-        <v>22</v>
+        <v>33</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -689,7 +689,7 @@
         <v>-162</v>
       </c>
       <c r="B39">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -697,7 +697,7 @@
         <v>-161</v>
       </c>
       <c r="B40">
-        <v>41</v>
+        <v>22</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -705,7 +705,7 @@
         <v>-160</v>
       </c>
       <c r="B41">
-        <v>27</v>
+        <v>19</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -713,7 +713,7 @@
         <v>-159</v>
       </c>
       <c r="B42">
-        <v>37</v>
+        <v>31</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -721,7 +721,7 @@
         <v>-158</v>
       </c>
       <c r="B43">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -729,7 +729,7 @@
         <v>-157</v>
       </c>
       <c r="B44">
-        <v>19</v>
+        <v>35</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -737,7 +737,7 @@
         <v>-156</v>
       </c>
       <c r="B45">
-        <v>31</v>
+        <v>39</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -745,7 +745,7 @@
         <v>-155</v>
       </c>
       <c r="B46">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -753,7 +753,7 @@
         <v>-154</v>
       </c>
       <c r="B47">
-        <v>34</v>
+        <v>28</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -761,7 +761,7 @@
         <v>-153</v>
       </c>
       <c r="B48">
-        <v>33</v>
+        <v>29</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -769,7 +769,7 @@
         <v>-152</v>
       </c>
       <c r="B49">
-        <v>30</v>
+        <v>37</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -785,7 +785,7 @@
         <v>-150</v>
       </c>
       <c r="B51">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -801,7 +801,7 @@
         <v>-148</v>
       </c>
       <c r="B53">
-        <v>34</v>
+        <v>26</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -809,7 +809,7 @@
         <v>-147</v>
       </c>
       <c r="B54">
-        <v>41</v>
+        <v>30</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -817,7 +817,7 @@
         <v>-146</v>
       </c>
       <c r="B55">
-        <v>39</v>
+        <v>22</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -825,7 +825,7 @@
         <v>-145</v>
       </c>
       <c r="B56">
-        <v>32</v>
+        <v>27</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -833,7 +833,7 @@
         <v>-144</v>
       </c>
       <c r="B57">
-        <v>33</v>
+        <v>37</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -841,7 +841,7 @@
         <v>-143</v>
       </c>
       <c r="B58">
-        <v>30</v>
+        <v>42</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -849,7 +849,7 @@
         <v>-142</v>
       </c>
       <c r="B59">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -857,7 +857,7 @@
         <v>-141</v>
       </c>
       <c r="B60">
-        <v>36</v>
+        <v>39</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -865,7 +865,7 @@
         <v>-140</v>
       </c>
       <c r="B61">
-        <v>40</v>
+        <v>33</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -873,7 +873,7 @@
         <v>-139</v>
       </c>
       <c r="B62">
-        <v>28</v>
+        <v>31</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -881,7 +881,7 @@
         <v>-138</v>
       </c>
       <c r="B63">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -889,7 +889,7 @@
         <v>-137</v>
       </c>
       <c r="B64">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -897,7 +897,7 @@
         <v>-136</v>
       </c>
       <c r="B65">
-        <v>29</v>
+        <v>41</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -905,7 +905,7 @@
         <v>-135</v>
       </c>
       <c r="B66">
-        <v>48</v>
+        <v>34</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -913,7 +913,7 @@
         <v>-134</v>
       </c>
       <c r="B67">
-        <v>47</v>
+        <v>44</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -921,7 +921,7 @@
         <v>-133</v>
       </c>
       <c r="B68">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -929,7 +929,7 @@
         <v>-132</v>
       </c>
       <c r="B69">
-        <v>47</v>
+        <v>33</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -937,7 +937,7 @@
         <v>-131</v>
       </c>
       <c r="B70">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -945,7 +945,7 @@
         <v>-130</v>
       </c>
       <c r="B71">
-        <v>37</v>
+        <v>33</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -953,7 +953,7 @@
         <v>-129</v>
       </c>
       <c r="B72">
-        <v>43</v>
+        <v>38</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -961,7 +961,7 @@
         <v>-128</v>
       </c>
       <c r="B73">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -969,7 +969,7 @@
         <v>-127</v>
       </c>
       <c r="B74">
-        <v>44</v>
+        <v>38</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -977,7 +977,7 @@
         <v>-126</v>
       </c>
       <c r="B75">
-        <v>31</v>
+        <v>35</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -985,7 +985,7 @@
         <v>-125</v>
       </c>
       <c r="B76">
-        <v>37</v>
+        <v>41</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -993,7 +993,7 @@
         <v>-124</v>
       </c>
       <c r="B77">
-        <v>31</v>
+        <v>35</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1001,7 +1001,7 @@
         <v>-123</v>
       </c>
       <c r="B78">
-        <v>50</v>
+        <v>45</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1009,7 +1009,7 @@
         <v>-122</v>
       </c>
       <c r="B79">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1017,7 +1017,7 @@
         <v>-121</v>
       </c>
       <c r="B80">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1025,7 +1025,7 @@
         <v>-120</v>
       </c>
       <c r="B81">
-        <v>40</v>
+        <v>48</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1033,7 +1033,7 @@
         <v>-119</v>
       </c>
       <c r="B82">
-        <v>35</v>
+        <v>52</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1041,7 +1041,7 @@
         <v>-118</v>
       </c>
       <c r="B83">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1049,7 +1049,7 @@
         <v>-117</v>
       </c>
       <c r="B84">
-        <v>28</v>
+        <v>33</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1057,7 +1057,7 @@
         <v>-116</v>
       </c>
       <c r="B85">
-        <v>40</v>
+        <v>44</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1065,7 +1065,7 @@
         <v>-115</v>
       </c>
       <c r="B86">
-        <v>42</v>
+        <v>35</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1073,7 +1073,7 @@
         <v>-114</v>
       </c>
       <c r="B87">
-        <v>29</v>
+        <v>23</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1081,7 +1081,7 @@
         <v>-113</v>
       </c>
       <c r="B88">
-        <v>37</v>
+        <v>33</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1089,7 +1089,7 @@
         <v>-112</v>
       </c>
       <c r="B89">
-        <v>41</v>
+        <v>27</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1097,7 +1097,7 @@
         <v>-111</v>
       </c>
       <c r="B90">
-        <v>31</v>
+        <v>39</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1105,7 +1105,7 @@
         <v>-110</v>
       </c>
       <c r="B91">
-        <v>26</v>
+        <v>34</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1113,7 +1113,7 @@
         <v>-109</v>
       </c>
       <c r="B92">
-        <v>46</v>
+        <v>39</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1121,7 +1121,7 @@
         <v>-108</v>
       </c>
       <c r="B93">
-        <v>37</v>
+        <v>49</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1137,7 +1137,7 @@
         <v>-106</v>
       </c>
       <c r="B95">
-        <v>41</v>
+        <v>44</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1145,7 +1145,7 @@
         <v>-105</v>
       </c>
       <c r="B96">
-        <v>42</v>
+        <v>38</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1153,7 +1153,7 @@
         <v>-104</v>
       </c>
       <c r="B97">
-        <v>42</v>
+        <v>23</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1161,7 +1161,7 @@
         <v>-103</v>
       </c>
       <c r="B98">
-        <v>44</v>
+        <v>39</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1169,7 +1169,7 @@
         <v>-102</v>
       </c>
       <c r="B99">
-        <v>29</v>
+        <v>35</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1177,7 +1177,7 @@
         <v>-101</v>
       </c>
       <c r="B100">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1185,7 +1185,7 @@
         <v>-100</v>
       </c>
       <c r="B101">
-        <v>37</v>
+        <v>40</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1193,7 +1193,7 @@
         <v>-99</v>
       </c>
       <c r="B102">
-        <v>32</v>
+        <v>46</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1209,7 +1209,7 @@
         <v>-97</v>
       </c>
       <c r="B104">
-        <v>25</v>
+        <v>36</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1217,7 +1217,7 @@
         <v>-96</v>
       </c>
       <c r="B105">
-        <v>42</v>
+        <v>38</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1225,7 +1225,7 @@
         <v>-95</v>
       </c>
       <c r="B106">
-        <v>38</v>
+        <v>50</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1233,7 +1233,7 @@
         <v>-94</v>
       </c>
       <c r="B107">
-        <v>43</v>
+        <v>40</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1241,7 +1241,7 @@
         <v>-93</v>
       </c>
       <c r="B108">
-        <v>28</v>
+        <v>39</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1257,7 +1257,7 @@
         <v>-91</v>
       </c>
       <c r="B110">
-        <v>34</v>
+        <v>44</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1273,7 +1273,7 @@
         <v>-89</v>
       </c>
       <c r="B112">
-        <v>47</v>
+        <v>35</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1281,7 +1281,7 @@
         <v>-88</v>
       </c>
       <c r="B113">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1289,7 +1289,7 @@
         <v>-87</v>
       </c>
       <c r="B114">
-        <v>41</v>
+        <v>50</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1297,7 +1297,7 @@
         <v>-86</v>
       </c>
       <c r="B115">
-        <v>47</v>
+        <v>37</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1305,7 +1305,7 @@
         <v>-85</v>
       </c>
       <c r="B116">
-        <v>33</v>
+        <v>49</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -1321,7 +1321,7 @@
         <v>-83</v>
       </c>
       <c r="B118">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="119" spans="1:2">
@@ -1329,7 +1329,7 @@
         <v>-82</v>
       </c>
       <c r="B119">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="120" spans="1:2">
@@ -1337,7 +1337,7 @@
         <v>-81</v>
       </c>
       <c r="B120">
-        <v>38</v>
+        <v>43</v>
       </c>
     </row>
     <row r="121" spans="1:2">
@@ -1345,7 +1345,7 @@
         <v>-80</v>
       </c>
       <c r="B121">
-        <v>36</v>
+        <v>42</v>
       </c>
     </row>
     <row r="122" spans="1:2">
@@ -1353,7 +1353,7 @@
         <v>-79</v>
       </c>
       <c r="B122">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="123" spans="1:2">
@@ -1361,7 +1361,7 @@
         <v>-78</v>
       </c>
       <c r="B123">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="124" spans="1:2">
@@ -1369,7 +1369,7 @@
         <v>-77</v>
       </c>
       <c r="B124">
-        <v>43</v>
+        <v>32</v>
       </c>
     </row>
     <row r="125" spans="1:2">
@@ -1377,7 +1377,7 @@
         <v>-76</v>
       </c>
       <c r="B125">
-        <v>31</v>
+        <v>46</v>
       </c>
     </row>
     <row r="126" spans="1:2">
@@ -1385,7 +1385,7 @@
         <v>-75</v>
       </c>
       <c r="B126">
-        <v>33</v>
+        <v>39</v>
       </c>
     </row>
     <row r="127" spans="1:2">
@@ -1393,7 +1393,7 @@
         <v>-74</v>
       </c>
       <c r="B127">
-        <v>39</v>
+        <v>45</v>
       </c>
     </row>
     <row r="128" spans="1:2">
@@ -1401,7 +1401,7 @@
         <v>-73</v>
       </c>
       <c r="B128">
-        <v>44</v>
+        <v>47</v>
       </c>
     </row>
     <row r="129" spans="1:2">
@@ -1409,7 +1409,7 @@
         <v>-72</v>
       </c>
       <c r="B129">
-        <v>36</v>
+        <v>40</v>
       </c>
     </row>
     <row r="130" spans="1:2">
@@ -1417,7 +1417,7 @@
         <v>-71</v>
       </c>
       <c r="B130">
-        <v>52</v>
+        <v>39</v>
       </c>
     </row>
     <row r="131" spans="1:2">
@@ -1425,7 +1425,7 @@
         <v>-70</v>
       </c>
       <c r="B131">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="132" spans="1:2">
@@ -1433,7 +1433,7 @@
         <v>-69</v>
       </c>
       <c r="B132">
-        <v>51</v>
+        <v>40</v>
       </c>
     </row>
     <row r="133" spans="1:2">
@@ -1441,7 +1441,7 @@
         <v>-68</v>
       </c>
       <c r="B133">
-        <v>50</v>
+        <v>47</v>
       </c>
     </row>
     <row r="134" spans="1:2">
@@ -1449,7 +1449,7 @@
         <v>-67</v>
       </c>
       <c r="B134">
-        <v>45</v>
+        <v>40</v>
       </c>
     </row>
     <row r="135" spans="1:2">
@@ -1457,7 +1457,7 @@
         <v>-66</v>
       </c>
       <c r="B135">
-        <v>33</v>
+        <v>60</v>
       </c>
     </row>
     <row r="136" spans="1:2">
@@ -1465,7 +1465,7 @@
         <v>-65</v>
       </c>
       <c r="B136">
-        <v>54</v>
+        <v>59</v>
       </c>
     </row>
     <row r="137" spans="1:2">
@@ -1473,7 +1473,7 @@
         <v>-64</v>
       </c>
       <c r="B137">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="138" spans="1:2">
@@ -1481,7 +1481,7 @@
         <v>-63</v>
       </c>
       <c r="B138">
-        <v>46</v>
+        <v>56</v>
       </c>
     </row>
     <row r="139" spans="1:2">
@@ -1489,7 +1489,7 @@
         <v>-62</v>
       </c>
       <c r="B139">
-        <v>55</v>
+        <v>47</v>
       </c>
     </row>
     <row r="140" spans="1:2">
@@ -1497,7 +1497,7 @@
         <v>-61</v>
       </c>
       <c r="B140">
-        <v>43</v>
+        <v>54</v>
       </c>
     </row>
     <row r="141" spans="1:2">
@@ -1505,7 +1505,7 @@
         <v>-60</v>
       </c>
       <c r="B141">
-        <v>57</v>
+        <v>37</v>
       </c>
     </row>
     <row r="142" spans="1:2">
@@ -1513,7 +1513,7 @@
         <v>-59</v>
       </c>
       <c r="B142">
-        <v>48</v>
+        <v>53</v>
       </c>
     </row>
     <row r="143" spans="1:2">
@@ -1521,7 +1521,7 @@
         <v>-58</v>
       </c>
       <c r="B143">
-        <v>43</v>
+        <v>55</v>
       </c>
     </row>
     <row r="144" spans="1:2">
@@ -1529,7 +1529,7 @@
         <v>-57</v>
       </c>
       <c r="B144">
-        <v>38</v>
+        <v>55</v>
       </c>
     </row>
     <row r="145" spans="1:2">
@@ -1537,7 +1537,7 @@
         <v>-56</v>
       </c>
       <c r="B145">
-        <v>47</v>
+        <v>44</v>
       </c>
     </row>
     <row r="146" spans="1:2">
@@ -1545,7 +1545,7 @@
         <v>-55</v>
       </c>
       <c r="B146">
-        <v>58</v>
+        <v>47</v>
       </c>
     </row>
     <row r="147" spans="1:2">
@@ -1553,7 +1553,7 @@
         <v>-54</v>
       </c>
       <c r="B147">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="148" spans="1:2">
@@ -1561,7 +1561,7 @@
         <v>-53</v>
       </c>
       <c r="B148">
-        <v>48</v>
+        <v>57</v>
       </c>
     </row>
     <row r="149" spans="1:2">
@@ -1569,7 +1569,7 @@
         <v>-52</v>
       </c>
       <c r="B149">
-        <v>44</v>
+        <v>61</v>
       </c>
     </row>
     <row r="150" spans="1:2">
@@ -1577,7 +1577,7 @@
         <v>-51</v>
       </c>
       <c r="B150">
-        <v>55</v>
+        <v>43</v>
       </c>
     </row>
     <row r="151" spans="1:2">
@@ -1585,7 +1585,7 @@
         <v>-50</v>
       </c>
       <c r="B151">
-        <v>49</v>
+        <v>53</v>
       </c>
     </row>
     <row r="152" spans="1:2">
@@ -1593,7 +1593,7 @@
         <v>-49</v>
       </c>
       <c r="B152">
-        <v>50</v>
+        <v>65</v>
       </c>
     </row>
     <row r="153" spans="1:2">
@@ -1601,7 +1601,7 @@
         <v>-48</v>
       </c>
       <c r="B153">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="154" spans="1:2">
@@ -1609,7 +1609,7 @@
         <v>-47</v>
       </c>
       <c r="B154">
-        <v>44</v>
+        <v>51</v>
       </c>
     </row>
     <row r="155" spans="1:2">
@@ -1617,7 +1617,7 @@
         <v>-46</v>
       </c>
       <c r="B155">
-        <v>42</v>
+        <v>55</v>
       </c>
     </row>
     <row r="156" spans="1:2">
@@ -1625,7 +1625,7 @@
         <v>-45</v>
       </c>
       <c r="B156">
-        <v>62</v>
+        <v>58</v>
       </c>
     </row>
     <row r="157" spans="1:2">
@@ -1633,7 +1633,7 @@
         <v>-44</v>
       </c>
       <c r="B157">
-        <v>62</v>
+        <v>56</v>
       </c>
     </row>
     <row r="158" spans="1:2">
@@ -1641,7 +1641,7 @@
         <v>-43</v>
       </c>
       <c r="B158">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="159" spans="1:2">
@@ -1649,7 +1649,7 @@
         <v>-42</v>
       </c>
       <c r="B159">
-        <v>61</v>
+        <v>46</v>
       </c>
     </row>
     <row r="160" spans="1:2">
@@ -1657,7 +1657,7 @@
         <v>-41</v>
       </c>
       <c r="B160">
-        <v>57</v>
+        <v>50</v>
       </c>
     </row>
     <row r="161" spans="1:2">
@@ -1665,7 +1665,7 @@
         <v>-40</v>
       </c>
       <c r="B161">
-        <v>68</v>
+        <v>52</v>
       </c>
     </row>
     <row r="162" spans="1:2">
@@ -1673,7 +1673,7 @@
         <v>-39</v>
       </c>
       <c r="B162">
-        <v>56</v>
+        <v>51</v>
       </c>
     </row>
     <row r="163" spans="1:2">
@@ -1681,7 +1681,7 @@
         <v>-38</v>
       </c>
       <c r="B163">
-        <v>60</v>
+        <v>52</v>
       </c>
     </row>
     <row r="164" spans="1:2">
@@ -1689,7 +1689,7 @@
         <v>-37</v>
       </c>
       <c r="B164">
-        <v>63</v>
+        <v>52</v>
       </c>
     </row>
     <row r="165" spans="1:2">
@@ -1697,7 +1697,7 @@
         <v>-36</v>
       </c>
       <c r="B165">
-        <v>56</v>
+        <v>73</v>
       </c>
     </row>
     <row r="166" spans="1:2">
@@ -1705,7 +1705,7 @@
         <v>-35</v>
       </c>
       <c r="B166">
-        <v>73</v>
+        <v>50</v>
       </c>
     </row>
     <row r="167" spans="1:2">
@@ -1713,7 +1713,7 @@
         <v>-34</v>
       </c>
       <c r="B167">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="168" spans="1:2">
@@ -1721,7 +1721,7 @@
         <v>-33</v>
       </c>
       <c r="B168">
-        <v>73</v>
+        <v>65</v>
       </c>
     </row>
     <row r="169" spans="1:2">
@@ -1729,7 +1729,7 @@
         <v>-32</v>
       </c>
       <c r="B169">
-        <v>53</v>
+        <v>70</v>
       </c>
     </row>
     <row r="170" spans="1:2">
@@ -1737,7 +1737,7 @@
         <v>-31</v>
       </c>
       <c r="B170">
-        <v>57</v>
+        <v>62</v>
       </c>
     </row>
     <row r="171" spans="1:2">
@@ -1745,7 +1745,7 @@
         <v>-30</v>
       </c>
       <c r="B171">
-        <v>70</v>
+        <v>72</v>
       </c>
     </row>
     <row r="172" spans="1:2">
@@ -1753,7 +1753,7 @@
         <v>-29</v>
       </c>
       <c r="B172">
-        <v>70</v>
+        <v>58</v>
       </c>
     </row>
     <row r="173" spans="1:2">
@@ -1761,7 +1761,7 @@
         <v>-28</v>
       </c>
       <c r="B173">
-        <v>73</v>
+        <v>68</v>
       </c>
     </row>
     <row r="174" spans="1:2">
@@ -1769,7 +1769,7 @@
         <v>-27</v>
       </c>
       <c r="B174">
-        <v>63</v>
+        <v>72</v>
       </c>
     </row>
     <row r="175" spans="1:2">
@@ -1777,7 +1777,7 @@
         <v>-26</v>
       </c>
       <c r="B175">
-        <v>65</v>
+        <v>59</v>
       </c>
     </row>
     <row r="176" spans="1:2">
@@ -1785,7 +1785,7 @@
         <v>-25</v>
       </c>
       <c r="B176">
-        <v>71</v>
+        <v>64</v>
       </c>
     </row>
     <row r="177" spans="1:2">
@@ -1793,7 +1793,7 @@
         <v>-24</v>
       </c>
       <c r="B177">
-        <v>100</v>
+        <v>66</v>
       </c>
     </row>
     <row r="178" spans="1:2">
@@ -1801,7 +1801,7 @@
         <v>-23</v>
       </c>
       <c r="B178">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="179" spans="1:2">
@@ -1809,7 +1809,7 @@
         <v>-22</v>
       </c>
       <c r="B179">
-        <v>76</v>
+        <v>81</v>
       </c>
     </row>
     <row r="180" spans="1:2">
@@ -1817,7 +1817,7 @@
         <v>-21</v>
       </c>
       <c r="B180">
-        <v>109</v>
+        <v>78</v>
       </c>
     </row>
     <row r="181" spans="1:2">
@@ -1833,7 +1833,7 @@
         <v>-19</v>
       </c>
       <c r="B182">
-        <v>121</v>
+        <v>80</v>
       </c>
     </row>
     <row r="183" spans="1:2">
@@ -1841,7 +1841,7 @@
         <v>-18</v>
       </c>
       <c r="B183">
-        <v>125</v>
+        <v>118</v>
       </c>
     </row>
     <row r="184" spans="1:2">
@@ -1849,7 +1849,7 @@
         <v>-17</v>
       </c>
       <c r="B184">
-        <v>114</v>
+        <v>111</v>
       </c>
     </row>
     <row r="185" spans="1:2">
@@ -1857,7 +1857,7 @@
         <v>-16</v>
       </c>
       <c r="B185">
-        <v>121</v>
+        <v>113</v>
       </c>
     </row>
     <row r="186" spans="1:2">
@@ -1865,7 +1865,7 @@
         <v>-15</v>
       </c>
       <c r="B186">
-        <v>110</v>
+        <v>95</v>
       </c>
     </row>
     <row r="187" spans="1:2">
@@ -1873,7 +1873,7 @@
         <v>-14</v>
       </c>
       <c r="B187">
-        <v>127</v>
+        <v>105</v>
       </c>
     </row>
     <row r="188" spans="1:2">
@@ -1881,7 +1881,7 @@
         <v>-13</v>
       </c>
       <c r="B188">
-        <v>144</v>
+        <v>134</v>
       </c>
     </row>
     <row r="189" spans="1:2">
@@ -1889,7 +1889,7 @@
         <v>-12</v>
       </c>
       <c r="B189">
-        <v>143</v>
+        <v>119</v>
       </c>
     </row>
     <row r="190" spans="1:2">
@@ -1897,7 +1897,7 @@
         <v>-11</v>
       </c>
       <c r="B190">
-        <v>142</v>
+        <v>128</v>
       </c>
     </row>
     <row r="191" spans="1:2">
@@ -1905,7 +1905,7 @@
         <v>-10</v>
       </c>
       <c r="B191">
-        <v>152</v>
+        <v>123</v>
       </c>
     </row>
     <row r="192" spans="1:2">
@@ -1913,7 +1913,7 @@
         <v>-9</v>
       </c>
       <c r="B192">
-        <v>165</v>
+        <v>171</v>
       </c>
     </row>
     <row r="193" spans="1:2">
@@ -1921,7 +1921,7 @@
         <v>-8</v>
       </c>
       <c r="B193">
-        <v>187</v>
+        <v>144</v>
       </c>
     </row>
     <row r="194" spans="1:2">
@@ -1929,7 +1929,7 @@
         <v>-7</v>
       </c>
       <c r="B194">
-        <v>208</v>
+        <v>181</v>
       </c>
     </row>
     <row r="195" spans="1:2">
@@ -1937,7 +1937,7 @@
         <v>-6</v>
       </c>
       <c r="B195">
-        <v>204</v>
+        <v>182</v>
       </c>
     </row>
     <row r="196" spans="1:2">
@@ -1945,7 +1945,7 @@
         <v>-5</v>
       </c>
       <c r="B196">
-        <v>237</v>
+        <v>206</v>
       </c>
     </row>
     <row r="197" spans="1:2">
@@ -1953,7 +1953,7 @@
         <v>-4</v>
       </c>
       <c r="B197">
-        <v>259</v>
+        <v>224</v>
       </c>
     </row>
     <row r="198" spans="1:2">
@@ -1961,7 +1961,7 @@
         <v>-3</v>
       </c>
       <c r="B198">
-        <v>263</v>
+        <v>236</v>
       </c>
     </row>
     <row r="199" spans="1:2">
@@ -1969,7 +1969,7 @@
         <v>-2</v>
       </c>
       <c r="B199">
-        <v>273</v>
+        <v>220</v>
       </c>
     </row>
     <row r="200" spans="1:2">
@@ -1977,7 +1977,7 @@
         <v>-1</v>
       </c>
       <c r="B200">
-        <v>281</v>
+        <v>271</v>
       </c>
     </row>
     <row r="201" spans="1:2">
@@ -1985,7 +1985,7 @@
         <v>0</v>
       </c>
       <c r="B201">
-        <v>291</v>
+        <v>569</v>
       </c>
     </row>
     <row r="202" spans="1:2">
@@ -1993,7 +1993,7 @@
         <v>1</v>
       </c>
       <c r="B202">
-        <v>327</v>
+        <v>311</v>
       </c>
     </row>
     <row r="203" spans="1:2">
@@ -2001,7 +2001,7 @@
         <v>2</v>
       </c>
       <c r="B203">
-        <v>307</v>
+        <v>304</v>
       </c>
     </row>
     <row r="204" spans="1:2">
@@ -2009,7 +2009,7 @@
         <v>3</v>
       </c>
       <c r="B204">
-        <v>364</v>
+        <v>332</v>
       </c>
     </row>
     <row r="205" spans="1:2">
@@ -2017,7 +2017,7 @@
         <v>4</v>
       </c>
       <c r="B205">
-        <v>401</v>
+        <v>365</v>
       </c>
     </row>
     <row r="206" spans="1:2">
@@ -2025,7 +2025,7 @@
         <v>5</v>
       </c>
       <c r="B206">
-        <v>404</v>
+        <v>414</v>
       </c>
     </row>
     <row r="207" spans="1:2">
@@ -2033,7 +2033,7 @@
         <v>6</v>
       </c>
       <c r="B207">
-        <v>417</v>
+        <v>448</v>
       </c>
     </row>
     <row r="208" spans="1:2">
@@ -2041,7 +2041,7 @@
         <v>7</v>
       </c>
       <c r="B208">
-        <v>463</v>
+        <v>456</v>
       </c>
     </row>
     <row r="209" spans="1:2">
@@ -2049,7 +2049,7 @@
         <v>8</v>
       </c>
       <c r="B209">
-        <v>447</v>
+        <v>466</v>
       </c>
     </row>
     <row r="210" spans="1:2">
@@ -2057,7 +2057,7 @@
         <v>9</v>
       </c>
       <c r="B210">
-        <v>496</v>
+        <v>493</v>
       </c>
     </row>
     <row r="211" spans="1:2">
@@ -2065,7 +2065,7 @@
         <v>10</v>
       </c>
       <c r="B211">
-        <v>522</v>
+        <v>516</v>
       </c>
     </row>
     <row r="212" spans="1:2">
@@ -2073,7 +2073,7 @@
         <v>11</v>
       </c>
       <c r="B212">
-        <v>552</v>
+        <v>536</v>
       </c>
     </row>
     <row r="213" spans="1:2">
@@ -2081,7 +2081,7 @@
         <v>12</v>
       </c>
       <c r="B213">
-        <v>592</v>
+        <v>586</v>
       </c>
     </row>
     <row r="214" spans="1:2">
@@ -2089,7 +2089,7 @@
         <v>13</v>
       </c>
       <c r="B214">
-        <v>611</v>
+        <v>628</v>
       </c>
     </row>
     <row r="215" spans="1:2">
@@ -2097,7 +2097,7 @@
         <v>14</v>
       </c>
       <c r="B215">
-        <v>626</v>
+        <v>622</v>
       </c>
     </row>
     <row r="216" spans="1:2">
@@ -2105,7 +2105,7 @@
         <v>15</v>
       </c>
       <c r="B216">
-        <v>633</v>
+        <v>671</v>
       </c>
     </row>
     <row r="217" spans="1:2">
@@ -2113,7 +2113,7 @@
         <v>16</v>
       </c>
       <c r="B217">
-        <v>665</v>
+        <v>672</v>
       </c>
     </row>
     <row r="218" spans="1:2">
@@ -2121,7 +2121,7 @@
         <v>17</v>
       </c>
       <c r="B218">
-        <v>697</v>
+        <v>695</v>
       </c>
     </row>
     <row r="219" spans="1:2">
@@ -2129,7 +2129,7 @@
         <v>18</v>
       </c>
       <c r="B219">
-        <v>732</v>
+        <v>735</v>
       </c>
     </row>
     <row r="220" spans="1:2">
@@ -2137,7 +2137,7 @@
         <v>19</v>
       </c>
       <c r="B220">
-        <v>741</v>
+        <v>710</v>
       </c>
     </row>
     <row r="221" spans="1:2">
@@ -2145,7 +2145,7 @@
         <v>20</v>
       </c>
       <c r="B221">
-        <v>765</v>
+        <v>771</v>
       </c>
     </row>
     <row r="222" spans="1:2">
@@ -2153,7 +2153,7 @@
         <v>21</v>
       </c>
       <c r="B222">
-        <v>790</v>
+        <v>758</v>
       </c>
     </row>
     <row r="223" spans="1:2">
@@ -2161,7 +2161,7 @@
         <v>22</v>
       </c>
       <c r="B223">
-        <v>815</v>
+        <v>807</v>
       </c>
     </row>
     <row r="224" spans="1:2">
@@ -2169,7 +2169,7 @@
         <v>23</v>
       </c>
       <c r="B224">
-        <v>837</v>
+        <v>848</v>
       </c>
     </row>
     <row r="225" spans="1:2">
@@ -2177,7 +2177,7 @@
         <v>24</v>
       </c>
       <c r="B225">
-        <v>855</v>
+        <v>883</v>
       </c>
     </row>
     <row r="226" spans="1:2">
@@ -2193,7 +2193,7 @@
         <v>26</v>
       </c>
       <c r="B227">
-        <v>882</v>
+        <v>930</v>
       </c>
     </row>
     <row r="228" spans="1:2">
@@ -2201,7 +2201,7 @@
         <v>27</v>
       </c>
       <c r="B228">
-        <v>915</v>
+        <v>909</v>
       </c>
     </row>
     <row r="229" spans="1:2">
@@ -2209,7 +2209,7 @@
         <v>28</v>
       </c>
       <c r="B229">
-        <v>895</v>
+        <v>893</v>
       </c>
     </row>
     <row r="230" spans="1:2">
@@ -2217,7 +2217,7 @@
         <v>29</v>
       </c>
       <c r="B230">
-        <v>883</v>
+        <v>967</v>
       </c>
     </row>
     <row r="231" spans="1:2">
@@ -2225,7 +2225,7 @@
         <v>30</v>
       </c>
       <c r="B231">
-        <v>950</v>
+        <v>979</v>
       </c>
     </row>
     <row r="232" spans="1:2">
@@ -2233,7 +2233,7 @@
         <v>31</v>
       </c>
       <c r="B232">
-        <v>935</v>
+        <v>989</v>
       </c>
     </row>
     <row r="233" spans="1:2">
@@ -2241,7 +2241,7 @@
         <v>32</v>
       </c>
       <c r="B233">
-        <v>962</v>
+        <v>968</v>
       </c>
     </row>
     <row r="234" spans="1:2">
@@ -2249,7 +2249,7 @@
         <v>33</v>
       </c>
       <c r="B234">
-        <v>1023</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="235" spans="1:2">
@@ -2257,7 +2257,7 @@
         <v>34</v>
       </c>
       <c r="B235">
-        <v>966</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="236" spans="1:2">
@@ -2265,7 +2265,7 @@
         <v>35</v>
       </c>
       <c r="B236">
-        <v>986</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="237" spans="1:2">
@@ -2273,7 +2273,7 @@
         <v>36</v>
       </c>
       <c r="B237">
-        <v>998</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="238" spans="1:2">
@@ -2281,7 +2281,7 @@
         <v>37</v>
       </c>
       <c r="B238">
-        <v>1065</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="239" spans="1:2">
@@ -2289,7 +2289,7 @@
         <v>38</v>
       </c>
       <c r="B239">
-        <v>1088</v>
+        <v>1077</v>
       </c>
     </row>
     <row r="240" spans="1:2">
@@ -2297,7 +2297,7 @@
         <v>39</v>
       </c>
       <c r="B240">
-        <v>1070</v>
+        <v>1132</v>
       </c>
     </row>
     <row r="241" spans="1:2">
@@ -2305,7 +2305,7 @@
         <v>40</v>
       </c>
       <c r="B241">
-        <v>1052</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="242" spans="1:2">
@@ -2313,7 +2313,7 @@
         <v>41</v>
       </c>
       <c r="B242">
-        <v>1082</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="243" spans="1:2">
@@ -2321,7 +2321,7 @@
         <v>42</v>
       </c>
       <c r="B243">
-        <v>1088</v>
+        <v>1146</v>
       </c>
     </row>
     <row r="244" spans="1:2">
@@ -2329,7 +2329,7 @@
         <v>43</v>
       </c>
       <c r="B244">
-        <v>1027</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="245" spans="1:2">
@@ -2337,7 +2337,7 @@
         <v>44</v>
       </c>
       <c r="B245">
-        <v>1037</v>
+        <v>1066</v>
       </c>
     </row>
     <row r="246" spans="1:2">
@@ -2345,7 +2345,7 @@
         <v>45</v>
       </c>
       <c r="B246">
-        <v>1058</v>
+        <v>1107</v>
       </c>
     </row>
     <row r="247" spans="1:2">
@@ -2353,7 +2353,7 @@
         <v>46</v>
       </c>
       <c r="B247">
-        <v>1026</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="248" spans="1:2">
@@ -2361,7 +2361,7 @@
         <v>47</v>
       </c>
       <c r="B248">
-        <v>1091</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="249" spans="1:2">
@@ -2369,7 +2369,7 @@
         <v>48</v>
       </c>
       <c r="B249">
-        <v>1086</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="250" spans="1:2">
@@ -2377,7 +2377,7 @@
         <v>49</v>
       </c>
       <c r="B250">
-        <v>1086</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="251" spans="1:2">
@@ -2385,7 +2385,7 @@
         <v>50</v>
       </c>
       <c r="B251">
-        <v>1063</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="252" spans="1:2">
@@ -2393,7 +2393,7 @@
         <v>51</v>
       </c>
       <c r="B252">
-        <v>1125</v>
+        <v>1108</v>
       </c>
     </row>
     <row r="253" spans="1:2">
@@ -2401,7 +2401,7 @@
         <v>52</v>
       </c>
       <c r="B253">
-        <v>1058</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="254" spans="1:2">
@@ -2409,7 +2409,7 @@
         <v>53</v>
       </c>
       <c r="B254">
-        <v>1148</v>
+        <v>1064</v>
       </c>
     </row>
     <row r="255" spans="1:2">
@@ -2417,7 +2417,7 @@
         <v>54</v>
       </c>
       <c r="B255">
-        <v>1047</v>
+        <v>1111</v>
       </c>
     </row>
     <row r="256" spans="1:2">
@@ -2425,7 +2425,7 @@
         <v>55</v>
       </c>
       <c r="B256">
-        <v>1037</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="257" spans="1:2">
@@ -2433,7 +2433,7 @@
         <v>56</v>
       </c>
       <c r="B257">
-        <v>1017</v>
+        <v>1096</v>
       </c>
     </row>
     <row r="258" spans="1:2">
@@ -2441,7 +2441,7 @@
         <v>57</v>
       </c>
       <c r="B258">
-        <v>1070</v>
+        <v>1082</v>
       </c>
     </row>
     <row r="259" spans="1:2">
@@ -2449,7 +2449,7 @@
         <v>58</v>
       </c>
       <c r="B259">
-        <v>1032</v>
+        <v>1046</v>
       </c>
     </row>
     <row r="260" spans="1:2">
@@ -2457,7 +2457,7 @@
         <v>59</v>
       </c>
       <c r="B260">
-        <v>1058</v>
+        <v>1088</v>
       </c>
     </row>
     <row r="261" spans="1:2">
@@ -2465,7 +2465,7 @@
         <v>60</v>
       </c>
       <c r="B261">
-        <v>1075</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="262" spans="1:2">
@@ -2473,7 +2473,7 @@
         <v>61</v>
       </c>
       <c r="B262">
-        <v>1090</v>
+        <v>1011</v>
       </c>
     </row>
     <row r="263" spans="1:2">
@@ -2481,7 +2481,7 @@
         <v>62</v>
       </c>
       <c r="B263">
-        <v>1010</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="264" spans="1:2">
@@ -2489,7 +2489,7 @@
         <v>63</v>
       </c>
       <c r="B264">
-        <v>998</v>
+        <v>987</v>
       </c>
     </row>
     <row r="265" spans="1:2">
@@ -2497,7 +2497,7 @@
         <v>64</v>
       </c>
       <c r="B265">
-        <v>973</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="266" spans="1:2">
@@ -2505,7 +2505,7 @@
         <v>65</v>
       </c>
       <c r="B266">
-        <v>1021</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="267" spans="1:2">
@@ -2513,7 +2513,7 @@
         <v>66</v>
       </c>
       <c r="B267">
-        <v>951</v>
+        <v>1069</v>
       </c>
     </row>
     <row r="268" spans="1:2">
@@ -2521,7 +2521,7 @@
         <v>67</v>
       </c>
       <c r="B268">
-        <v>1008</v>
+        <v>944</v>
       </c>
     </row>
     <row r="269" spans="1:2">
@@ -2529,7 +2529,7 @@
         <v>68</v>
       </c>
       <c r="B269">
-        <v>981</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="270" spans="1:2">
@@ -2537,7 +2537,7 @@
         <v>69</v>
       </c>
       <c r="B270">
-        <v>978</v>
+        <v>932</v>
       </c>
     </row>
     <row r="271" spans="1:2">
@@ -2545,7 +2545,7 @@
         <v>70</v>
       </c>
       <c r="B271">
-        <v>908</v>
+        <v>927</v>
       </c>
     </row>
     <row r="272" spans="1:2">
@@ -2553,7 +2553,7 @@
         <v>71</v>
       </c>
       <c r="B272">
-        <v>941</v>
+        <v>949</v>
       </c>
     </row>
     <row r="273" spans="1:2">
@@ -2561,7 +2561,7 @@
         <v>72</v>
       </c>
       <c r="B273">
-        <v>960</v>
+        <v>950</v>
       </c>
     </row>
     <row r="274" spans="1:2">
@@ -2569,7 +2569,7 @@
         <v>73</v>
       </c>
       <c r="B274">
-        <v>856</v>
+        <v>904</v>
       </c>
     </row>
     <row r="275" spans="1:2">
@@ -2577,7 +2577,7 @@
         <v>74</v>
       </c>
       <c r="B275">
-        <v>912</v>
+        <v>896</v>
       </c>
     </row>
     <row r="276" spans="1:2">
@@ -2585,7 +2585,7 @@
         <v>75</v>
       </c>
       <c r="B276">
-        <v>843</v>
+        <v>901</v>
       </c>
     </row>
     <row r="277" spans="1:2">
@@ -2593,7 +2593,7 @@
         <v>76</v>
       </c>
       <c r="B277">
-        <v>847</v>
+        <v>912</v>
       </c>
     </row>
     <row r="278" spans="1:2">
@@ -2601,7 +2601,7 @@
         <v>77</v>
       </c>
       <c r="B278">
-        <v>836</v>
+        <v>780</v>
       </c>
     </row>
     <row r="279" spans="1:2">
@@ -2609,7 +2609,7 @@
         <v>78</v>
       </c>
       <c r="B279">
-        <v>843</v>
+        <v>818</v>
       </c>
     </row>
     <row r="280" spans="1:2">
@@ -2617,7 +2617,7 @@
         <v>79</v>
       </c>
       <c r="B280">
-        <v>821</v>
+        <v>755</v>
       </c>
     </row>
     <row r="281" spans="1:2">
@@ -2625,7 +2625,7 @@
         <v>80</v>
       </c>
       <c r="B281">
-        <v>793</v>
+        <v>757</v>
       </c>
     </row>
     <row r="282" spans="1:2">
@@ -2633,7 +2633,7 @@
         <v>81</v>
       </c>
       <c r="B282">
-        <v>755</v>
+        <v>735</v>
       </c>
     </row>
     <row r="283" spans="1:2">
@@ -2641,7 +2641,7 @@
         <v>82</v>
       </c>
       <c r="B283">
-        <v>692</v>
+        <v>773</v>
       </c>
     </row>
     <row r="284" spans="1:2">
@@ -2649,7 +2649,7 @@
         <v>83</v>
       </c>
       <c r="B284">
-        <v>712</v>
+        <v>669</v>
       </c>
     </row>
     <row r="285" spans="1:2">
@@ -2657,7 +2657,7 @@
         <v>84</v>
       </c>
       <c r="B285">
-        <v>705</v>
+        <v>653</v>
       </c>
     </row>
     <row r="286" spans="1:2">
@@ -2665,7 +2665,7 @@
         <v>85</v>
       </c>
       <c r="B286">
-        <v>678</v>
+        <v>681</v>
       </c>
     </row>
     <row r="287" spans="1:2">
@@ -2673,7 +2673,7 @@
         <v>86</v>
       </c>
       <c r="B287">
-        <v>730</v>
+        <v>680</v>
       </c>
     </row>
     <row r="288" spans="1:2">
@@ -2681,7 +2681,7 @@
         <v>87</v>
       </c>
       <c r="B288">
-        <v>656</v>
+        <v>652</v>
       </c>
     </row>
     <row r="289" spans="1:2">
@@ -2689,7 +2689,7 @@
         <v>88</v>
       </c>
       <c r="B289">
-        <v>641</v>
+        <v>613</v>
       </c>
     </row>
     <row r="290" spans="1:2">
@@ -2697,7 +2697,7 @@
         <v>89</v>
       </c>
       <c r="B290">
-        <v>561</v>
+        <v>597</v>
       </c>
     </row>
     <row r="291" spans="1:2">
@@ -2705,7 +2705,7 @@
         <v>90</v>
       </c>
       <c r="B291">
-        <v>567</v>
+        <v>554</v>
       </c>
     </row>
     <row r="292" spans="1:2">
@@ -2713,7 +2713,7 @@
         <v>91</v>
       </c>
       <c r="B292">
-        <v>543</v>
+        <v>577</v>
       </c>
     </row>
     <row r="293" spans="1:2">
@@ -2721,7 +2721,7 @@
         <v>92</v>
       </c>
       <c r="B293">
-        <v>546</v>
+        <v>523</v>
       </c>
     </row>
     <row r="294" spans="1:2">
@@ -2729,7 +2729,7 @@
         <v>93</v>
       </c>
       <c r="B294">
-        <v>537</v>
+        <v>479</v>
       </c>
     </row>
     <row r="295" spans="1:2">
@@ -2737,7 +2737,7 @@
         <v>94</v>
       </c>
       <c r="B295">
-        <v>483</v>
+        <v>513</v>
       </c>
     </row>
     <row r="296" spans="1:2">
@@ -2745,7 +2745,7 @@
         <v>95</v>
       </c>
       <c r="B296">
-        <v>472</v>
+        <v>501</v>
       </c>
     </row>
     <row r="297" spans="1:2">
@@ -2753,7 +2753,7 @@
         <v>96</v>
       </c>
       <c r="B297">
-        <v>444</v>
+        <v>476</v>
       </c>
     </row>
     <row r="298" spans="1:2">
@@ -2761,7 +2761,7 @@
         <v>97</v>
       </c>
       <c r="B298">
-        <v>411</v>
+        <v>456</v>
       </c>
     </row>
     <row r="299" spans="1:2">
@@ -2769,7 +2769,7 @@
         <v>98</v>
       </c>
       <c r="B299">
-        <v>447</v>
+        <v>415</v>
       </c>
     </row>
     <row r="300" spans="1:2">
@@ -2777,7 +2777,7 @@
         <v>99</v>
       </c>
       <c r="B300">
-        <v>389</v>
+        <v>404</v>
       </c>
     </row>
     <row r="301" spans="1:2">
@@ -2785,7 +2785,7 @@
         <v>100</v>
       </c>
       <c r="B301">
-        <v>400</v>
+        <v>367</v>
       </c>
     </row>
     <row r="302" spans="1:2">
@@ -2793,7 +2793,7 @@
         <v>101</v>
       </c>
       <c r="B302">
-        <v>393</v>
+        <v>343</v>
       </c>
     </row>
     <row r="303" spans="1:2">
@@ -2801,7 +2801,7 @@
         <v>102</v>
       </c>
       <c r="B303">
-        <v>364</v>
+        <v>332</v>
       </c>
     </row>
     <row r="304" spans="1:2">
@@ -2809,7 +2809,7 @@
         <v>103</v>
       </c>
       <c r="B304">
-        <v>373</v>
+        <v>314</v>
       </c>
     </row>
     <row r="305" spans="1:2">
@@ -2817,7 +2817,7 @@
         <v>104</v>
       </c>
       <c r="B305">
-        <v>297</v>
+        <v>300</v>
       </c>
     </row>
     <row r="306" spans="1:2">
@@ -2825,7 +2825,7 @@
         <v>105</v>
       </c>
       <c r="B306">
-        <v>290</v>
+        <v>274</v>
       </c>
     </row>
     <row r="307" spans="1:2">
@@ -2833,7 +2833,7 @@
         <v>106</v>
       </c>
       <c r="B307">
-        <v>302</v>
+        <v>266</v>
       </c>
     </row>
     <row r="308" spans="1:2">
@@ -2841,7 +2841,7 @@
         <v>107</v>
       </c>
       <c r="B308">
-        <v>288</v>
+        <v>268</v>
       </c>
     </row>
     <row r="309" spans="1:2">
@@ -2849,7 +2849,7 @@
         <v>108</v>
       </c>
       <c r="B309">
-        <v>292</v>
+        <v>244</v>
       </c>
     </row>
     <row r="310" spans="1:2">
@@ -2857,7 +2857,7 @@
         <v>109</v>
       </c>
       <c r="B310">
-        <v>270</v>
+        <v>229</v>
       </c>
     </row>
     <row r="311" spans="1:2">
@@ -2865,7 +2865,7 @@
         <v>110</v>
       </c>
       <c r="B311">
-        <v>224</v>
+        <v>226</v>
       </c>
     </row>
     <row r="312" spans="1:2">
@@ -2873,7 +2873,7 @@
         <v>111</v>
       </c>
       <c r="B312">
-        <v>227</v>
+        <v>237</v>
       </c>
     </row>
     <row r="313" spans="1:2">
@@ -2881,7 +2881,7 @@
         <v>112</v>
       </c>
       <c r="B313">
-        <v>233</v>
+        <v>236</v>
       </c>
     </row>
     <row r="314" spans="1:2">
@@ -2889,7 +2889,7 @@
         <v>113</v>
       </c>
       <c r="B314">
-        <v>197</v>
+        <v>217</v>
       </c>
     </row>
     <row r="315" spans="1:2">
@@ -2897,7 +2897,7 @@
         <v>114</v>
       </c>
       <c r="B315">
-        <v>225</v>
+        <v>194</v>
       </c>
     </row>
     <row r="316" spans="1:2">
@@ -2905,7 +2905,7 @@
         <v>115</v>
       </c>
       <c r="B316">
-        <v>202</v>
+        <v>178</v>
       </c>
     </row>
     <row r="317" spans="1:2">
@@ -2913,7 +2913,7 @@
         <v>116</v>
       </c>
       <c r="B317">
-        <v>222</v>
+        <v>168</v>
       </c>
     </row>
     <row r="318" spans="1:2">
@@ -2921,7 +2921,7 @@
         <v>117</v>
       </c>
       <c r="B318">
-        <v>183</v>
+        <v>178</v>
       </c>
     </row>
     <row r="319" spans="1:2">
@@ -2929,7 +2929,7 @@
         <v>118</v>
       </c>
       <c r="B319">
-        <v>184</v>
+        <v>145</v>
       </c>
     </row>
     <row r="320" spans="1:2">
@@ -2937,7 +2937,7 @@
         <v>119</v>
       </c>
       <c r="B320">
-        <v>177</v>
+        <v>183</v>
       </c>
     </row>
     <row r="321" spans="1:2">
@@ -2945,7 +2945,7 @@
         <v>120</v>
       </c>
       <c r="B321">
-        <v>139</v>
+        <v>131</v>
       </c>
     </row>
     <row r="322" spans="1:2">
@@ -2953,7 +2953,7 @@
         <v>121</v>
       </c>
       <c r="B322">
-        <v>145</v>
+        <v>140</v>
       </c>
     </row>
     <row r="323" spans="1:2">
@@ -2961,7 +2961,7 @@
         <v>122</v>
       </c>
       <c r="B323">
-        <v>147</v>
+        <v>131</v>
       </c>
     </row>
     <row r="324" spans="1:2">
@@ -2969,7 +2969,7 @@
         <v>123</v>
       </c>
       <c r="B324">
-        <v>145</v>
+        <v>134</v>
       </c>
     </row>
     <row r="325" spans="1:2">
@@ -2977,7 +2977,7 @@
         <v>124</v>
       </c>
       <c r="B325">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="326" spans="1:2">
@@ -2985,7 +2985,7 @@
         <v>125</v>
       </c>
       <c r="B326">
-        <v>118</v>
+        <v>92</v>
       </c>
     </row>
     <row r="327" spans="1:2">
@@ -2993,7 +2993,7 @@
         <v>126</v>
       </c>
       <c r="B327">
-        <v>126</v>
+        <v>111</v>
       </c>
     </row>
     <row r="328" spans="1:2">
@@ -3001,7 +3001,7 @@
         <v>127</v>
       </c>
       <c r="B328">
-        <v>102</v>
+        <v>110</v>
       </c>
     </row>
     <row r="329" spans="1:2">
@@ -3009,7 +3009,7 @@
         <v>128</v>
       </c>
       <c r="B329">
-        <v>111</v>
+        <v>115</v>
       </c>
     </row>
     <row r="330" spans="1:2">
@@ -3017,7 +3017,7 @@
         <v>129</v>
       </c>
       <c r="B330">
-        <v>114</v>
+        <v>87</v>
       </c>
     </row>
     <row r="331" spans="1:2">
@@ -3025,7 +3025,7 @@
         <v>130</v>
       </c>
       <c r="B331">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="332" spans="1:2">
@@ -3033,7 +3033,7 @@
         <v>131</v>
       </c>
       <c r="B332">
-        <v>100</v>
+        <v>67</v>
       </c>
     </row>
     <row r="333" spans="1:2">
@@ -3041,7 +3041,7 @@
         <v>132</v>
       </c>
       <c r="B333">
-        <v>89</v>
+        <v>83</v>
       </c>
     </row>
     <row r="334" spans="1:2">
@@ -3049,7 +3049,7 @@
         <v>133</v>
       </c>
       <c r="B334">
-        <v>80</v>
+        <v>85</v>
       </c>
     </row>
     <row r="335" spans="1:2">
@@ -3057,7 +3057,7 @@
         <v>134</v>
       </c>
       <c r="B335">
-        <v>105</v>
+        <v>73</v>
       </c>
     </row>
     <row r="336" spans="1:2">
@@ -3065,7 +3065,7 @@
         <v>135</v>
       </c>
       <c r="B336">
-        <v>80</v>
+        <v>87</v>
       </c>
     </row>
     <row r="337" spans="1:2">
@@ -3073,7 +3073,7 @@
         <v>136</v>
       </c>
       <c r="B337">
-        <v>72</v>
+        <v>67</v>
       </c>
     </row>
     <row r="338" spans="1:2">
@@ -3081,7 +3081,7 @@
         <v>137</v>
       </c>
       <c r="B338">
-        <v>67</v>
+        <v>85</v>
       </c>
     </row>
     <row r="339" spans="1:2">
@@ -3089,7 +3089,7 @@
         <v>138</v>
       </c>
       <c r="B339">
-        <v>76</v>
+        <v>65</v>
       </c>
     </row>
     <row r="340" spans="1:2">
@@ -3097,7 +3097,7 @@
         <v>139</v>
       </c>
       <c r="B340">
-        <v>75</v>
+        <v>70</v>
       </c>
     </row>
     <row r="341" spans="1:2">
@@ -3105,7 +3105,7 @@
         <v>140</v>
       </c>
       <c r="B341">
-        <v>75</v>
+        <v>65</v>
       </c>
     </row>
     <row r="342" spans="1:2">
@@ -3113,7 +3113,7 @@
         <v>141</v>
       </c>
       <c r="B342">
-        <v>75</v>
+        <v>67</v>
       </c>
     </row>
     <row r="343" spans="1:2">
@@ -3121,7 +3121,7 @@
         <v>142</v>
       </c>
       <c r="B343">
-        <v>52</v>
+        <v>62</v>
       </c>
     </row>
     <row r="344" spans="1:2">
@@ -3129,7 +3129,7 @@
         <v>143</v>
       </c>
       <c r="B344">
-        <v>49</v>
+        <v>61</v>
       </c>
     </row>
     <row r="345" spans="1:2">
@@ -3137,7 +3137,7 @@
         <v>144</v>
       </c>
       <c r="B345">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="346" spans="1:2">
@@ -3145,7 +3145,7 @@
         <v>145</v>
       </c>
       <c r="B346">
-        <v>57</v>
+        <v>60</v>
       </c>
     </row>
     <row r="347" spans="1:2">
@@ -3153,7 +3153,7 @@
         <v>146</v>
       </c>
       <c r="B347">
-        <v>61</v>
+        <v>51</v>
       </c>
     </row>
     <row r="348" spans="1:2">
@@ -3161,7 +3161,7 @@
         <v>147</v>
       </c>
       <c r="B348">
-        <v>51</v>
+        <v>54</v>
       </c>
     </row>
     <row r="349" spans="1:2">
@@ -3169,7 +3169,7 @@
         <v>148</v>
       </c>
       <c r="B349">
-        <v>63</v>
+        <v>49</v>
       </c>
     </row>
     <row r="350" spans="1:2">
@@ -3177,7 +3177,7 @@
         <v>149</v>
       </c>
       <c r="B350">
-        <v>44</v>
+        <v>49</v>
       </c>
     </row>
     <row r="351" spans="1:2">
@@ -3193,7 +3193,7 @@
         <v>151</v>
       </c>
       <c r="B352">
-        <v>30</v>
+        <v>40</v>
       </c>
     </row>
     <row r="353" spans="1:2">
@@ -3201,7 +3201,7 @@
         <v>152</v>
       </c>
       <c r="B353">
-        <v>49</v>
+        <v>36</v>
       </c>
     </row>
     <row r="354" spans="1:2">
@@ -3209,7 +3209,7 @@
         <v>153</v>
       </c>
       <c r="B354">
-        <v>40</v>
+        <v>36</v>
       </c>
     </row>
     <row r="355" spans="1:2">
@@ -3225,7 +3225,7 @@
         <v>155</v>
       </c>
       <c r="B356">
-        <v>33</v>
+        <v>39</v>
       </c>
     </row>
     <row r="357" spans="1:2">
@@ -3233,7 +3233,7 @@
         <v>156</v>
       </c>
       <c r="B357">
-        <v>36</v>
+        <v>30</v>
       </c>
     </row>
     <row r="358" spans="1:2">
@@ -3241,7 +3241,7 @@
         <v>157</v>
       </c>
       <c r="B358">
-        <v>35</v>
+        <v>29</v>
       </c>
     </row>
     <row r="359" spans="1:2">
@@ -3249,7 +3249,7 @@
         <v>158</v>
       </c>
       <c r="B359">
-        <v>34</v>
+        <v>28</v>
       </c>
     </row>
     <row r="360" spans="1:2">
@@ -3257,7 +3257,7 @@
         <v>159</v>
       </c>
       <c r="B360">
-        <v>28</v>
+        <v>34</v>
       </c>
     </row>
     <row r="361" spans="1:2">
@@ -3265,7 +3265,7 @@
         <v>160</v>
       </c>
       <c r="B361">
-        <v>42</v>
+        <v>23</v>
       </c>
     </row>
     <row r="362" spans="1:2">
@@ -3273,7 +3273,7 @@
         <v>161</v>
       </c>
       <c r="B362">
-        <v>29</v>
+        <v>21</v>
       </c>
     </row>
     <row r="363" spans="1:2">
@@ -3281,7 +3281,7 @@
         <v>162</v>
       </c>
       <c r="B363">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="364" spans="1:2">
@@ -3297,7 +3297,7 @@
         <v>164</v>
       </c>
       <c r="B365">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="366" spans="1:2">
@@ -3305,7 +3305,7 @@
         <v>165</v>
       </c>
       <c r="B366">
-        <v>17</v>
+        <v>27</v>
       </c>
     </row>
     <row r="367" spans="1:2">
@@ -3313,7 +3313,7 @@
         <v>166</v>
       </c>
       <c r="B367">
-        <v>19</v>
+        <v>29</v>
       </c>
     </row>
     <row r="368" spans="1:2">
@@ -3321,7 +3321,7 @@
         <v>167</v>
       </c>
       <c r="B368">
-        <v>21</v>
+        <v>16</v>
       </c>
     </row>
     <row r="369" spans="1:2">
@@ -3329,7 +3329,7 @@
         <v>168</v>
       </c>
       <c r="B369">
-        <v>24</v>
+        <v>21</v>
       </c>
     </row>
     <row r="370" spans="1:2">
@@ -3337,7 +3337,7 @@
         <v>169</v>
       </c>
       <c r="B370">
-        <v>14</v>
+        <v>26</v>
       </c>
     </row>
     <row r="371" spans="1:2">
@@ -3345,7 +3345,7 @@
         <v>170</v>
       </c>
       <c r="B371">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="372" spans="1:2">
@@ -3353,7 +3353,7 @@
         <v>171</v>
       </c>
       <c r="B372">
-        <v>28</v>
+        <v>16</v>
       </c>
     </row>
     <row r="373" spans="1:2">
@@ -3361,7 +3361,7 @@
         <v>172</v>
       </c>
       <c r="B373">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="374" spans="1:2">
@@ -3369,7 +3369,7 @@
         <v>173</v>
       </c>
       <c r="B374">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="375" spans="1:2">
@@ -3377,7 +3377,7 @@
         <v>174</v>
       </c>
       <c r="B375">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="376" spans="1:2">
@@ -3385,7 +3385,7 @@
         <v>175</v>
       </c>
       <c r="B376">
-        <v>19</v>
+        <v>10</v>
       </c>
     </row>
     <row r="377" spans="1:2">
@@ -3393,7 +3393,7 @@
         <v>176</v>
       </c>
       <c r="B377">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="378" spans="1:2">
@@ -3401,7 +3401,7 @@
         <v>177</v>
       </c>
       <c r="B378">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="379" spans="1:2">
@@ -3409,7 +3409,7 @@
         <v>178</v>
       </c>
       <c r="B379">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="380" spans="1:2">
@@ -3417,7 +3417,7 @@
         <v>179</v>
       </c>
       <c r="B380">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="381" spans="1:2">
@@ -3425,7 +3425,7 @@
         <v>180</v>
       </c>
       <c r="B381">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="382" spans="1:2">
@@ -3433,7 +3433,7 @@
         <v>181</v>
       </c>
       <c r="B382">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="383" spans="1:2">
@@ -3449,7 +3449,7 @@
         <v>183</v>
       </c>
       <c r="B384">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="385" spans="1:2">
@@ -3457,7 +3457,7 @@
         <v>184</v>
       </c>
       <c r="B385">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="386" spans="1:2">
@@ -3473,7 +3473,7 @@
         <v>186</v>
       </c>
       <c r="B387">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="388" spans="1:2">
@@ -3481,7 +3481,7 @@
         <v>187</v>
       </c>
       <c r="B388">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="389" spans="1:2">
@@ -3489,7 +3489,7 @@
         <v>188</v>
       </c>
       <c r="B389">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="390" spans="1:2">
@@ -3497,7 +3497,7 @@
         <v>189</v>
       </c>
       <c r="B390">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="391" spans="1:2">
@@ -3505,7 +3505,7 @@
         <v>190</v>
       </c>
       <c r="B391">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="392" spans="1:2">
@@ -3513,7 +3513,7 @@
         <v>191</v>
       </c>
       <c r="B392">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="393" spans="1:2">
@@ -3521,7 +3521,7 @@
         <v>192</v>
       </c>
       <c r="B393">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="394" spans="1:2">
@@ -3529,7 +3529,7 @@
         <v>193</v>
       </c>
       <c r="B394">
-        <v>1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="395" spans="1:2">
@@ -3537,7 +3537,7 @@
         <v>194</v>
       </c>
       <c r="B395">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="396" spans="1:2">
@@ -3545,7 +3545,7 @@
         <v>195</v>
       </c>
       <c r="B396">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="397" spans="1:2">
@@ -3553,7 +3553,7 @@
         <v>196</v>
       </c>
       <c r="B397">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="398" spans="1:2">
@@ -3561,7 +3561,7 @@
         <v>197</v>
       </c>
       <c r="B398">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="399" spans="1:2">
@@ -3569,7 +3569,7 @@
         <v>198</v>
       </c>
       <c r="B399">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="400" spans="1:2">
@@ -3577,7 +3577,7 @@
         <v>199</v>
       </c>
       <c r="B400">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
